--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,49 +799,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131694581</v>
+        <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>96783</v>
+        <v>92322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 11756, Hallingeberg, Sm</t>
+          <t>A11756 Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575282</v>
+        <v>575591</v>
       </c>
       <c r="R3" t="n">
-        <v>6410867</v>
+        <v>6410909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,12 +871,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +897,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694581</t>
+          <t>https://artportalen.se/Sighting/136693610</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136586800</v>
+        <v>131694581</v>
       </c>
       <c r="B4" t="n">
-        <v>92316</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,34 +925,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3008</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575495</v>
+        <v>575282</v>
       </c>
       <c r="R4" t="n">
-        <v>6411043</v>
+        <v>6410867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1009,22 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586800</t>
+          <t>https://artportalen.se/Sighting/131694581</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136586822</v>
+        <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92780</v>
+        <v>92319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>3008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,7 +1056,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575348</v>
+        <v>575495</v>
       </c>
       <c r="R5" t="n">
-        <v>6411222</v>
+        <v>6411043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,42 +1129,50 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586822</t>
+          <t>https://artportalen.se/Sighting/136586800</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132023887</v>
+        <v>136586822</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>92783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575349</v>
+        <v>575348</v>
       </c>
       <c r="R6" t="n">
-        <v>6410779</v>
+        <v>6411222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,17 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal torr tallåga</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1237,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023887</t>
+          <t>https://artportalen.se/Sighting/136586822</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136586852</v>
+        <v>132023887</v>
       </c>
       <c r="B7" t="n">
-        <v>58019</v>
+        <v>79992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,31 +1260,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575083</v>
+        <v>575349</v>
       </c>
       <c r="R7" t="n">
-        <v>6411042</v>
+        <v>6410779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,17 +1317,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I mycket klen murken/död björk</t>
+          <t>På gammal torr tallåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,39 +1348,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586852</t>
+          <t>https://artportalen.se/Sighting/132023887</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131694507</v>
+        <v>136586852</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1388,16 +1388,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1407,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575330</v>
+        <v>575083</v>
       </c>
       <c r="R8" t="n">
-        <v>6410861</v>
+        <v>6411042</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,12 +1433,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I mycket klen murken/död björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,19 +1463,19 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694507</t>
+          <t>https://artportalen.se/Sighting/136586852</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131694784</v>
+        <v>131694507</v>
       </c>
       <c r="B9" t="n">
         <v>57972</v>
@@ -1502,12 +1503,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1517,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575261</v>
+        <v>575330</v>
       </c>
       <c r="R9" t="n">
-        <v>6410922</v>
+        <v>6410861</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,11 +1558,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,13 +1583,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694784</t>
+          <t>https://artportalen.se/Sighting/131694507</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132023787</v>
+        <v>131694784</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575602</v>
+        <v>575261</v>
       </c>
       <c r="R10" t="n">
-        <v>6410868</v>
+        <v>6410922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,13 +1698,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023787</t>
+          <t>https://artportalen.se/Sighting/131694784</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132023830</v>
+        <v>132023787</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575339</v>
+        <v>575602</v>
       </c>
       <c r="R11" t="n">
-        <v>6411131</v>
+        <v>6410868</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,13 +1813,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023830</t>
+          <t>https://artportalen.se/Sighting/132023787</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132023856</v>
+        <v>132023830</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1852,7 +1852,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575228</v>
+        <v>575339</v>
       </c>
       <c r="R12" t="n">
-        <v>6410830</v>
+        <v>6411131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,50 +1928,46 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023856</t>
+          <t>https://artportalen.se/Sighting/132023830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694377</v>
+        <v>132023856</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1981,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575366</v>
+        <v>575228</v>
       </c>
       <c r="R13" t="n">
-        <v>6410831</v>
+        <v>6410830</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,12 +2007,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,13 +2043,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694377</t>
+          <t>https://artportalen.se/Sighting/132023856</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131694554</v>
+        <v>131694377</v>
       </c>
       <c r="B14" t="n">
         <v>58136</v>
@@ -2085,7 +2086,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2095,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575283</v>
+        <v>575366</v>
       </c>
       <c r="R14" t="n">
-        <v>6410851</v>
+        <v>6410831</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2156,16 +2157,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694554</t>
+          <t>https://artportalen.se/Sighting/131694377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136586928</v>
+        <v>131694554</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,14 +2193,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2209,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575493</v>
+        <v>575283</v>
       </c>
       <c r="R15" t="n">
-        <v>6411010</v>
+        <v>6410851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,12 +2240,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,52 +2265,56 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586928</t>
+          <t>https://artportalen.se/Sighting/131694554</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136586933</v>
+        <v>136586928</v>
       </c>
       <c r="B16" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2380,16 +2385,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586933</t>
+          <t>https://artportalen.se/Sighting/136586928</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132023743</v>
+        <v>136586933</v>
       </c>
       <c r="B17" t="n">
-        <v>111257</v>
+        <v>58162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,27 +2402,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2425,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575597</v>
+        <v>575493</v>
       </c>
       <c r="R17" t="n">
-        <v>6410871</v>
+        <v>6411010</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,17 +2464,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 tallar med mycket murgröna</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,7 +2478,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2486,52 +2489,48 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023743</t>
+          <t>https://artportalen.se/Sighting/136586933</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131694345</v>
+        <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>111257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2541,13 +2540,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575355</v>
+        <v>575597</v>
       </c>
       <c r="R18" t="n">
-        <v>6410850</v>
+        <v>6410871</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2571,12 +2570,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 tallar med mycket murgröna</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,13 +2607,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694345</t>
+          <t>https://artportalen.se/Sighting/132023743</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131694439</v>
+        <v>131694345</v>
       </c>
       <c r="B19" t="n">
         <v>99195</v>
@@ -2652,10 +2656,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575317</v>
+        <v>575355</v>
       </c>
       <c r="R19" t="n">
-        <v>6410866</v>
+        <v>6410850</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,13 +2718,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694439</t>
+          <t>https://artportalen.se/Sighting/131694345</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131694622</v>
+        <v>131694439</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2763,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575286</v>
+        <v>575317</v>
       </c>
       <c r="R20" t="n">
-        <v>6410869</v>
+        <v>6410866</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,13 +2829,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694622</t>
+          <t>https://artportalen.se/Sighting/131694439</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131694753</v>
+        <v>131694622</v>
       </c>
       <c r="B21" t="n">
         <v>99195</v>
@@ -2874,10 +2878,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575284</v>
+        <v>575286</v>
       </c>
       <c r="R21" t="n">
-        <v>6410886</v>
+        <v>6410869</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,13 +2940,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694753</t>
+          <t>https://artportalen.se/Sighting/131694622</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131694893</v>
+        <v>131694753</v>
       </c>
       <c r="B22" t="n">
         <v>99195</v>
@@ -2985,10 +2989,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575372</v>
+        <v>575284</v>
       </c>
       <c r="R22" t="n">
-        <v>6410835</v>
+        <v>6410886</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,13 +3051,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694893</t>
+          <t>https://artportalen.se/Sighting/131694753</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131694940</v>
+        <v>131694893</v>
       </c>
       <c r="B23" t="n">
         <v>99195</v>
@@ -3096,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575407</v>
+        <v>575372</v>
       </c>
       <c r="R23" t="n">
-        <v>6410979</v>
+        <v>6410835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3158,13 +3162,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694940</t>
+          <t>https://artportalen.se/Sighting/131694893</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B24" t="n">
         <v>99195</v>
@@ -3207,10 +3211,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R24" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3269,13 +3273,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694954</t>
+          <t>https://artportalen.se/Sighting/131694940</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131694986</v>
+        <v>131694954</v>
       </c>
       <c r="B25" t="n">
         <v>99195</v>
@@ -3318,10 +3322,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575403</v>
+        <v>575453</v>
       </c>
       <c r="R25" t="n">
-        <v>6411051</v>
+        <v>6410987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,6 +3383,117 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694954</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131694986</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 11756, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575403</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6411051</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131694986</t>
         </is>
@@ -3410,6 +3525,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92322</v>
+        <v>92323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92322</v>
+        <v>92323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136586822</v>
+        <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92783</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575348</v>
+        <v>575592</v>
       </c>
       <c r="R6" t="n">
-        <v>6411222</v>
+        <v>6410909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,12 +1211,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Samma låga som laxporing</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,48 +1242,56 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586822</t>
+          <t>https://artportalen.se/Sighting/136715216</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132023887</v>
+        <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1287,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575349</v>
+        <v>575348</v>
       </c>
       <c r="R7" t="n">
-        <v>6410779</v>
+        <v>6411222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,17 +1330,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal torr tallåga</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,22 +1356,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023887</t>
+          <t>https://artportalen.se/Sighting/136586822</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136586852</v>
+        <v>132023887</v>
       </c>
       <c r="B8" t="n">
-        <v>58019</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,31 +1379,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575083</v>
+        <v>575349</v>
       </c>
       <c r="R8" t="n">
-        <v>6411042</v>
+        <v>6410779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,17 +1436,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I mycket klen murken/död björk</t>
+          <t>På gammal torr tallåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,6 +1455,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,39 +1467,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586852</t>
+          <t>https://artportalen.se/Sighting/132023887</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131694507</v>
+        <v>136586852</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>58019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1503,16 +1507,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575330</v>
+        <v>575083</v>
       </c>
       <c r="R9" t="n">
-        <v>6410861</v>
+        <v>6411042</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,12 +1552,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I mycket klen murken/död björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,19 +1582,19 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694507</t>
+          <t>https://artportalen.se/Sighting/136586852</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131694784</v>
+        <v>131694507</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1617,12 +1622,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1632,13 +1641,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575261</v>
+        <v>575330</v>
       </c>
       <c r="R10" t="n">
-        <v>6410922</v>
+        <v>6410861</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,11 +1677,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,13 +1702,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694784</t>
+          <t>https://artportalen.se/Sighting/131694507</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132023787</v>
+        <v>131694784</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1747,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575602</v>
+        <v>575261</v>
       </c>
       <c r="R11" t="n">
-        <v>6410868</v>
+        <v>6410922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,17 +1781,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,13 +1817,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023787</t>
+          <t>https://artportalen.se/Sighting/131694784</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132023830</v>
+        <v>132023787</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1862,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575339</v>
+        <v>575602</v>
       </c>
       <c r="R12" t="n">
-        <v>6411131</v>
+        <v>6410868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,13 +1932,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023830</t>
+          <t>https://artportalen.se/Sighting/132023787</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132023856</v>
+        <v>132023830</v>
       </c>
       <c r="B13" t="n">
         <v>57972</v>
@@ -1967,7 +1971,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1977,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575228</v>
+        <v>575339</v>
       </c>
       <c r="R13" t="n">
-        <v>6410830</v>
+        <v>6411131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,50 +2047,46 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023856</t>
+          <t>https://artportalen.se/Sighting/132023830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131694377</v>
+        <v>132023856</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2096,13 +2096,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575366</v>
+        <v>575228</v>
       </c>
       <c r="R14" t="n">
-        <v>6410831</v>
+        <v>6410830</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,12 +2126,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,13 +2162,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694377</t>
+          <t>https://artportalen.se/Sighting/132023856</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131694554</v>
+        <v>131694377</v>
       </c>
       <c r="B15" t="n">
         <v>58136</v>
@@ -2200,7 +2205,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2210,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575283</v>
+        <v>575366</v>
       </c>
       <c r="R15" t="n">
-        <v>6410851</v>
+        <v>6410831</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,16 +2276,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694554</t>
+          <t>https://artportalen.se/Sighting/131694377</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136586928</v>
+        <v>131694554</v>
       </c>
       <c r="B16" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,14 +2312,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2324,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575493</v>
+        <v>575283</v>
       </c>
       <c r="R16" t="n">
-        <v>6411010</v>
+        <v>6410851</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2354,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,52 +2384,56 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586928</t>
+          <t>https://artportalen.se/Sighting/131694554</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136586933</v>
+        <v>136586928</v>
       </c>
       <c r="B17" t="n">
-        <v>58162</v>
+        <v>58167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2495,16 +2504,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136586933</t>
+          <t>https://artportalen.se/Sighting/136586928</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132023743</v>
+        <v>136586933</v>
       </c>
       <c r="B18" t="n">
-        <v>111257</v>
+        <v>58162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,27 +2521,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219677</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2540,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575597</v>
+        <v>575493</v>
       </c>
       <c r="R18" t="n">
-        <v>6410871</v>
+        <v>6411010</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2570,17 +2583,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 tallar med mycket murgröna</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,7 +2597,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2601,52 +2608,48 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132023743</t>
+          <t>https://artportalen.se/Sighting/136586933</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131694345</v>
+        <v>132023743</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>111257</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2656,13 +2659,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575355</v>
+        <v>575597</v>
       </c>
       <c r="R19" t="n">
-        <v>6410850</v>
+        <v>6410871</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,12 +2689,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 tallar med mycket murgröna</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,13 +2726,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694345</t>
+          <t>https://artportalen.se/Sighting/132023743</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131694439</v>
+        <v>131694345</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2767,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575317</v>
+        <v>575355</v>
       </c>
       <c r="R20" t="n">
-        <v>6410866</v>
+        <v>6410850</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,13 +2837,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694439</t>
+          <t>https://artportalen.se/Sighting/131694345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131694622</v>
+        <v>131694439</v>
       </c>
       <c r="B21" t="n">
         <v>99195</v>
@@ -2878,10 +2886,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575286</v>
+        <v>575317</v>
       </c>
       <c r="R21" t="n">
-        <v>6410869</v>
+        <v>6410866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,13 +2948,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694622</t>
+          <t>https://artportalen.se/Sighting/131694439</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131694753</v>
+        <v>131694622</v>
       </c>
       <c r="B22" t="n">
         <v>99195</v>
@@ -2989,10 +2997,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575284</v>
+        <v>575286</v>
       </c>
       <c r="R22" t="n">
-        <v>6410886</v>
+        <v>6410869</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,13 +3059,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694753</t>
+          <t>https://artportalen.se/Sighting/131694622</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131694893</v>
+        <v>131694753</v>
       </c>
       <c r="B23" t="n">
         <v>99195</v>
@@ -3100,10 +3108,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575372</v>
+        <v>575284</v>
       </c>
       <c r="R23" t="n">
-        <v>6410835</v>
+        <v>6410886</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,13 +3170,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694893</t>
+          <t>https://artportalen.se/Sighting/131694753</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131694940</v>
+        <v>131694893</v>
       </c>
       <c r="B24" t="n">
         <v>99195</v>
@@ -3211,10 +3219,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575407</v>
+        <v>575372</v>
       </c>
       <c r="R24" t="n">
-        <v>6410979</v>
+        <v>6410835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,13 +3281,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694940</t>
+          <t>https://artportalen.se/Sighting/131694893</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B25" t="n">
         <v>99195</v>
@@ -3322,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R25" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3384,13 +3392,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694954</t>
+          <t>https://artportalen.se/Sighting/131694940</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131694986</v>
+        <v>131694954</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3433,10 +3441,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575403</v>
+        <v>575453</v>
       </c>
       <c r="R26" t="n">
-        <v>6411051</v>
+        <v>6410987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,6 +3502,117 @@
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694954</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131694986</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 11756, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>575403</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6411051</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131694986</t>
         </is>
@@ -3526,6 +3645,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92323</v>
+        <v>92328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92323</v>
+        <v>92328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92320</v>
+        <v>92325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92320</v>
+        <v>92325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136586852</v>
       </c>
       <c r="B9" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136586928</v>
       </c>
       <c r="B17" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>136586933</v>
       </c>
       <c r="B18" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92330</v>
+        <v>92332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92330</v>
+        <v>92332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92332</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92332</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92341</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92341</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136586648</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92345</v>
+        <v>92347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136586800</v>
       </c>
       <c r="B5" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
         <v>136586822</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92347</v>
+        <v>92360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92360</v>
+        <v>92362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136693610</v>
       </c>
       <c r="B3" t="n">
-        <v>92362</v>
+        <v>92365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>136715216</v>
       </c>
       <c r="B6" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
